--- a/artfynd/A 16469-2023 artfynd.xlsx
+++ b/artfynd/A 16469-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16469-2023 artfynd.xlsx
+++ b/artfynd/A 16469-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>104160759</v>
       </c>
       <c r="B2" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549365.1106590288</v>
+        <v>549366</v>
       </c>
       <c r="R2" t="n">
-        <v>6376508.764988168</v>
+        <v>6376509</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103437049</v>
+        <v>104161227</v>
       </c>
       <c r="B3" t="n">
-        <v>99566</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,27 +795,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221317</v>
+        <v>799</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Ögonvaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Cuphophyllus fuscescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Bres.) Bon</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549570.8693672653</v>
+        <v>549431</v>
       </c>
       <c r="R3" t="n">
-        <v>6376356.619731385</v>
+        <v>6376412</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,27 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>vägkant</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103437321</v>
+        <v>103436747</v>
       </c>
       <c r="B4" t="n">
-        <v>44332</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102020</v>
+        <v>101256</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Mindre purpurmätare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Lythria cruentaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>(Hufnagel, 1767)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549410.0686067103</v>
+        <v>549526</v>
       </c>
       <c r="R4" t="n">
-        <v>6376439.505282871</v>
+        <v>6376367</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,19 +974,9 @@
           <t>2022-06-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,6 +1001,678 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>103436765</v>
+      </c>
+      <c r="B5" t="n">
+        <v>45046</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102020</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Smalsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Zygaena osterodensis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Reiss, 1921</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hultsfreds flygplats, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>549703</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6376302</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lönneberga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>103437321</v>
+      </c>
+      <c r="B6" t="n">
+        <v>45046</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102020</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Smalsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Zygaena osterodensis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reiss, 1921</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hultsfreds flygplats, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>549410</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6376440</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lönneberga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>103436758</v>
+      </c>
+      <c r="B7" t="n">
+        <v>43309</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hultsfreds flygplats, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>549698</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6376301</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lönneberga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103437058</v>
+      </c>
+      <c r="B8" t="n">
+        <v>43309</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hultsfreds flygplats, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>549410</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6376440</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lönneberga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134237025</v>
+      </c>
+      <c r="B9" t="n">
+        <v>43314</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fagerhult, Fagerhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>549377</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6376436</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lönneberga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Petter Sjöström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Petter Sjöström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>103437049</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hultsfreds flygplats, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>549571</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6376356</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lönneberga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16469-2023 artfynd.xlsx
+++ b/artfynd/A 16469-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104160759</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104161227</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103436747</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103436765</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103437321</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103436758</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103437058</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134237025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1673,8 +1718,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103437049</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>